--- a/20260806_権限設定_ヘルプページ.xlsx
+++ b/20260806_権限設定_ヘルプページ.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ヘルプページ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$243</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$248</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C243"/>
+  <dimension ref="A1:C248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1769,10 +1769,14 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>&gt; 区分は先に決めてください。区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr"/>
+          <t>&gt; 権限名は他と重ならないようにしてください</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>すでにある権限と同じ名前では保存できません。「別名で保存してください」と表示されたら、別の名前を入力してください。同じ名前が並ぶと、割り当てるときにどちらを選べばよいか分からなくなるためです。</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -1782,62 +1786,66 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
+          <t>&gt; 区分は先に決めてください</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>区分によって設定できる画面が変わります。保存したあとに区分を変更することはできません。別の区分の権限が必要になった場合は、新しく作成してください。「既存の権限をコピー」を使うと、設定を引き継いだうえで区分だけ変えられます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
           <t>&gt; 会社と店舗の両方の画面を使う場合は、権限を2つ作ってください。1つの権限で会社画面と店舗画面の両方を扱うことはできません。たとえば経理の方が「お支払い（会社画面）」と「費用設定・予算設定（店舗画面）」の両方を見る場合、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="16" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B92" s="17" t="inlineStr">
+      <c r="B93" s="17" t="inlineStr">
         <is>
           <t>STEP 4　画面ごとに設定して保存する</t>
         </is>
       </c>
-      <c r="C92" s="16" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="C93" s="16" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>画面ごとに「操作」「閲覧」「なし」を選び、「保存」を選択します。保存すると権限一覧に戻ります。</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="12" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B94" s="13" t="inlineStr">
+      <c r="B95" s="13" t="inlineStr">
         <is>
           <t>設定 ｜ できること</t>
         </is>
       </c>
-      <c r="C94" s="12" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr"/>
+      <c r="C95" s="12" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -1847,7 +1855,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>閲覧 ｜ 画面を開けます</t>
+          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr"/>
@@ -1860,131 +1868,131 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
+          <t>閲覧 ｜ 画面を開けます</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
           <t>なし ｜ 画面が表示されません</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>&gt; 「閲覧」と「操作」は、今回のリリースではどちらも画面を開けるかどうかの設定として動作します。「閲覧」を選んだ場合に画面内の変更操作を禁止する制御は、次回以降のリリースで対応予定です。変更させたくない方には、その画面を「なし」に設定してください。</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>「操作」は「閲覧」を含みます。「操作」を選ぶと「閲覧」も自動的に有効になります。</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="15" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B100" s="15" t="inlineStr">
+      <c r="B101" s="15" t="inlineStr">
         <is>
           <t>【画像④】</t>
         </is>
       </c>
-      <c r="C100" s="15" t="inlineStr">
+      <c r="C101" s="15" t="inlineStr">
         <is>
           <t>画面ごとの設定（操作／閲覧／なし）　※スクリーンショット未取得（撮影リスト ④ 番）</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>&gt; さらに細かく設定することもできます。画面名を選択すると、その画面の中の機能や、表示する数字（指標）を個別に設定できます。</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>続けてメンバーに割り当てる場合は、「保存」ではなく「🔗 ユーザー割当で紐付け →」を選択します。</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="10" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B103" s="11" t="inlineStr">
+      <c r="B104" s="11" t="inlineStr">
         <is>
           <t>権限をメンバーに割り当てる</t>
         </is>
       </c>
-      <c r="C103" s="10" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="C104" s="10" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>作成した権限は、メンバーに割り当てて初めて有効になります。割り当て方法は3つあり、目的に応じて使い分けます。始める画面と、保存後に開く画面がそれぞれ違います。</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="12" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="12" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B105" s="13" t="inlineStr">
+      <c r="B106" s="13" t="inlineStr">
         <is>
           <t>方法 ｜ 始める画面 ｜ 保存後に開く画面</t>
         </is>
       </c>
-      <c r="C105" s="12" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>方法1　まとめて割り当てる ｜ 権限の設定画面 ｜ 役割サマリ</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr"/>
+      <c r="C106" s="12" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -1994,7 +2002,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>方法2　メンバーを選んで割り当てる ｜ ユーザー割当 ｜ ユーザー割当</t>
+          <t>方法1　まとめて割り当てる ｜ 権限の設定画面 ｜ 役割サマリ</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr"/>
@@ -2007,7 +2015,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>方法3　権限から探して割り当てる ｜ 役割サマリ ｜ ユーザー割当（絞り込みは保たれます）</t>
+          <t>方法2　メンバーを選んで割り当てる ｜ ユーザー割当 ｜ ユーザー割当</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr"/>
@@ -2015,41 +2023,41 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
+          <t>方法3　権限から探して割り当てる ｜ 役割サマリ ｜ ユーザー割当（絞り込みは保たれます）</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
           <t>「役割サマリ」は、権限ごとに何名へ割り当てているかを確認する画面です。</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="16" t="inlineStr">
+      <c r="C110" s="4" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B110" s="17" t="inlineStr">
+      <c r="B111" s="17" t="inlineStr">
         <is>
           <t>方法1　まとめて割り当てる（権限を作った直後におすすめ）</t>
         </is>
       </c>
-      <c r="C110" s="16" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限の設定画面の下部で「🔗 ユーザー割当で紐付け →」を選択する</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr"/>
+      <c r="C111" s="16" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -2059,7 +2067,7 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>2. 割り当てる方の「含める」にチェックを入れる</t>
+          <t>1. 権限の設定画面の下部で「🔗 ユーザー割当で紐付け →」を選択する</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr"/>
@@ -2072,7 +2080,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>3. 店舗の権限の場合は、あわせて担当店舗を選ぶ</t>
+          <t>2. 割り当てる方の「含める」にチェックを入れる</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr"/>
@@ -2085,7 +2093,7 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>4. 「保存」を選択する</t>
+          <t>3. 店舗の権限の場合は、あわせて担当店舗を選ぶ</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr"/>
@@ -2093,45 +2101,45 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
+          <t>4. 「保存」を選択する</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
           <t>保存すると役割サマリが開き、割り当てた権限が強調表示されます。</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="15" t="inlineStr">
+      <c r="C116" s="4" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B116" s="15" t="inlineStr">
+      <c r="B117" s="15" t="inlineStr">
         <is>
           <t>【画像⑤】</t>
         </is>
       </c>
-      <c r="C116" s="15" t="inlineStr">
+      <c r="C117" s="15" t="inlineStr">
         <is>
           <t>まとめて割り当てる画面　※スクリーンショット未取得（撮影リスト ⑤ 番）</t>
         </is>
       </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>&gt; すでに別の権限をお持ちの方については、1人が持てる権限が1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
-        </is>
-      </c>
-      <c r="C117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -2141,36 +2149,36 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
+          <t>&gt; すでに別の権限をお持ちの方については、1人が持てる権限が1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
           <t>&gt; 対象は自動で絞り込まれます。店舗の権限を割り当てるときは店舗所属の方、会社の権限を割り当てるときは本部所属の方が表示されます。全員から選びたい場合は「すべて表示」を選択してください。</t>
         </is>
       </c>
-      <c r="C118" s="5" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="16" t="inlineStr">
+      <c r="C119" s="5" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B119" s="17" t="inlineStr">
+      <c r="B120" s="17" t="inlineStr">
         <is>
           <t>方法2　メンバーを選んで割り当てる（入社・異動のとき）</t>
         </is>
       </c>
-      <c r="C119" s="16" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限設定画面の上部で「ユーザー割当」を選択する</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="inlineStr"/>
+      <c r="C120" s="16" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -2180,7 +2188,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>2. 対象の方の行で「割当を編集」を選択する</t>
+          <t>1. 権限設定画面の上部で「ユーザー割当」を選択する</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr"/>
@@ -2193,7 +2201,7 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>3. 権限を1つ選ぶ</t>
+          <t>2. 対象の方の行で「割当を編集」を選択する</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr"/>
@@ -2206,7 +2214,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>4. 「保存」を選択する</t>
+          <t>3. 権限を1つ選ぶ</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr"/>
@@ -2214,58 +2222,58 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
+          <t>4. 「保存」を選択する</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
           <t>保存するとユーザー割当に戻ります。</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="15" t="inlineStr">
+      <c r="C125" s="4" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B125" s="15" t="inlineStr">
+      <c r="B126" s="15" t="inlineStr">
         <is>
           <t>【画像⑥】</t>
         </is>
       </c>
-      <c r="C125" s="15" t="inlineStr">
+      <c r="C126" s="15" t="inlineStr">
         <is>
           <t>メンバーごとの割当編集画面　※スクリーンショット未取得（撮影リスト ⑥ 番）</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="16" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B126" s="17" t="inlineStr">
+      <c r="B127" s="17" t="inlineStr">
         <is>
           <t>方法3　権限から探して割り当てる（保持者を確認したいとき）</t>
         </is>
       </c>
-      <c r="C126" s="16" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限設定画面の上部で「役割サマリ」を選択する</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr"/>
+      <c r="C127" s="16" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -2275,7 +2283,7 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>2. 対象の権限の「割当へ →」を選択する</t>
+          <t>1. 権限設定画面の上部で「役割サマリ」を選択する</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr"/>
@@ -2288,7 +2296,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>3. その権限をお持ちの方に絞り込まれた状態でユーザー割当が開く</t>
+          <t>2. 対象の権限の「割当へ →」を選択する</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr"/>
@@ -2301,7 +2309,7 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>4. 対象の方の行で「割当を編集」→「保存」を選択する</t>
+          <t>3. その権限をお持ちの方に絞り込まれた状態でユーザー割当が開く</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr"/>
@@ -2309,41 +2317,41 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
+          <t>4. 対象の方の行で「割当を編集」→「保存」を選択する</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
           <t>絞り込みは保たれたままです。</t>
         </is>
       </c>
-      <c r="C131" s="4" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="10" t="inlineStr">
+      <c r="C132" s="4" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B132" s="11" t="inlineStr">
+      <c r="B133" s="11" t="inlineStr">
         <is>
           <t>担当店舗を設定する</t>
         </is>
       </c>
-      <c r="C132" s="10" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="inlineStr"/>
+      <c r="C133" s="10" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -2353,50 +2361,50 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
+          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
           <t>どの店舗の数字を見せるかは、権限ではなく人ごとに決めます。 同じ「店長」の権限でも、渋谷店の店長には渋谷店を、新宿店の店長には新宿店を設定します。</t>
         </is>
       </c>
-      <c r="C134" s="4" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="14" t="inlineStr">
+      <c r="C135" s="4" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="14" t="inlineStr">
         <is>
           <t>図</t>
         </is>
       </c>
-      <c r="B135" s="14" t="inlineStr">
+      <c r="B136" s="14" t="inlineStr">
         <is>
           <t>【図2】</t>
         </is>
       </c>
-      <c r="C135" s="14" t="inlineStr">
+      <c r="C136" s="14" t="inlineStr">
         <is>
           <t>権限と担当店舗の関係　※作成済み。help/figures/ の SVG または PNG を掲載</t>
         </is>
       </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B136" s="4" t="inlineStr">
-        <is>
-          <t>店舗の権限（区分が「店舗」の権限）を割り当てると、担当店舗の選択欄が表示されます。</t>
-        </is>
-      </c>
-      <c r="C136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>1. 割当編集の画面で、店舗の権限を選択する</t>
+          <t>店舗の権限（区分が「店舗」の権限）を割り当てると、担当店舗の選択欄が表示されます。</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr"/>
@@ -2409,7 +2417,7 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>2. 「対象店舗」で担当店舗を選ぶ</t>
+          <t>1. 割当編集の画面で、店舗の権限を選択する</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr"/>
@@ -2422,7 +2430,7 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れる</t>
+          <t>2. 「対象店舗」で担当店舗を選ぶ</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr"/>
@@ -2435,7 +2443,7 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>4. 「保存」を選択する</t>
+          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れる</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr"/>
@@ -2443,32 +2451,28 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
+          <t>4. 「保存」を選択する</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
           <t>担当店舗は複数選択できます。保存するとユーザー割当に戻ります。</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B142" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑦】</t>
-        </is>
-      </c>
-      <c r="C142" s="15" t="inlineStr">
-        <is>
-          <t>担当店舗の選択画面　※スクリーンショット未取得（撮影リスト ⑦ 番）</t>
-        </is>
-      </c>
+      <c r="C142" s="4" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
@@ -2478,75 +2482,87 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
+          <t>&gt; 「全店」を選ぶと、あとから増えた店舗も対象になります</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>店舗を新しく追加したとき、「全店」を選んでいる方は自動的にその店舗も見られるようになります。設定し直す必要はありません。特定の店舗だけを見せたい場合は「全店」ではなく店舗を個別に選んでください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 閉店した店舗の設定は残ります</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>店舗を閉店にしても、担当店舗の設定はそのまま残ります。担当店舗が空になることはありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B145" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑦】</t>
+        </is>
+      </c>
+      <c r="C145" s="15" t="inlineStr">
+        <is>
+          <t>担当店舗の選択画面　※スクリーンショット未取得（撮影リスト ⑦ 番）</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
           <t>&gt; 担当店舗は必ず1つ以上お選びください。店舗の権限で担当店舗が未設定の場合、保存できません。また、権限の設定画面に「⚠ ◯名が店舗未設定」と表示されます。</t>
         </is>
       </c>
-      <c r="C143" s="5" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B144" s="4" t="inlineStr">
+      <c r="C146" s="5" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
         <is>
           <t>会社の権限は全社が対象となるため、担当店舗の設定は不要です。</t>
         </is>
       </c>
-      <c r="C144" s="4" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="5" t="inlineStr">
+      <c r="C147" s="4" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B145" s="6" t="inlineStr">
+      <c r="B148" s="6" t="inlineStr">
         <is>
           <t>&gt; 今回のリリースでは、担当店舗は割り当ての記録として保存されます。担当外の店舗のデータを画面に出さない制御は、次回以降のリリースで対応予定です。</t>
         </is>
       </c>
-      <c r="C145" s="5" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B146" s="4" t="inlineStr">
-        <is>
-          <t>ここまでで初期設定は完了です。 以降は、見せる数字をさらに絞りたいとき、権限を直したいとき、異動・退職で付け替えたいときにお読みください。</t>
-        </is>
-      </c>
-      <c r="C146" s="4" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B147" s="11" t="inlineStr">
-        <is>
-          <t>表示する数字を選ぶ</t>
-        </is>
-      </c>
-      <c r="C147" s="10" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B148" s="4" t="inlineStr">
-        <is>
-          <t>同じ画面でも、表示する数字（指標）を権限ごとに選べます。</t>
-        </is>
-      </c>
-      <c r="C148" s="4" t="inlineStr"/>
+      <c r="C148" s="5" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -2556,33 +2572,33 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>流れ — 権限一覧 →「指標一覧」→ 店舗／会社のタブを切り替えて選ぶ → その場で反映（保存ボタンはありません）</t>
+          <t>ここまでで初期設定は完了です。 以降は、見せる数字をさらに絞りたいとき、権限を直したいとき、異動・退職で付け替えたいときにお読みください。</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
-        </is>
-      </c>
-      <c r="C150" s="5" t="inlineStr"/>
+      <c r="A150" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B150" s="11" t="inlineStr">
+        <is>
+          <t>表示する数字を選ぶ</t>
+        </is>
+      </c>
+      <c r="C150" s="10" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択する</t>
+          <t>同じ画面でも、表示する数字（指標）を権限ごとに選べます。</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr"/>
@@ -2590,71 +2606,67 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替える</t>
+          <t>流れ — 権限一覧 →「指標一覧」→ 店舗／会社のタブを切り替えて選ぶ → その場で反映（保存ボタンはありません）</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>3. 各項目を選択して、表示／非表示を切り替える</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="inlineStr"/>
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>保存操作は不要で、その場で反映されます。</t>
+          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択する</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B155" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑧】</t>
-        </is>
-      </c>
-      <c r="C155" s="15" t="inlineStr">
-        <is>
-          <t>指標一覧の画面　※スクリーンショット未取得（撮影リスト ⑧ 番）</t>
-        </is>
-      </c>
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替える</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B156" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 初期値は自動で設定されます。権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
-        </is>
-      </c>
-      <c r="C156" s="5" t="inlineStr"/>
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>3. 各項目を選択して、表示／非表示を切り替える</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -2664,36 +2676,40 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>項目が多い場合は「指標条件設定」が便利です。 「指標条件設定 ＞」から、おすすめの組み合わせ（現場スタッフ向け／店長向け／管理者・経理向け）を選んで一括設定できます。この画面だけは「適用して指標一覧へ」を選ぶまで反映されません。「キャンセル」を選ぶと、変更は破棄されて指標一覧に戻ります。</t>
+          <t>保存操作は不要で、その場で反映されます。</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="inlineStr">
-        <is>
-          <t>作った組み合わせは「名前をつけて保存」するとマイテンプレートに登録されます。他の権限を設定するときに読み込めるので、同じ組み合わせを作り直す必要はありません。保存した組み合わせは更新・削除もできます。</t>
-        </is>
-      </c>
-      <c r="C158" s="4" t="inlineStr"/>
+      <c r="A158" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B158" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑧】</t>
+        </is>
+      </c>
+      <c r="C158" s="15" t="inlineStr">
+        <is>
+          <t>指標一覧の画面　※スクリーンショット未取得（撮影リスト ⑧ 番）</t>
+        </is>
+      </c>
     </row>
     <row r="159">
-      <c r="A159" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B159" s="11" t="inlineStr">
-        <is>
-          <t>作成した権限を修正する</t>
-        </is>
-      </c>
-      <c r="C159" s="10" t="inlineStr"/>
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 初期値は自動で設定されます。権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -2703,62 +2719,62 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>作成済みの権限は、いくつかの入口から修正できます。どこから入っても同じ編集画面が開き、保存すると元いた画面に戻ります。</t>
+          <t>項目が多い場合は「指標条件設定」が便利です。 「指標条件設定 ＞」から、おすすめの組み合わせ（現場スタッフ向け／店長向け／管理者・経理向け）を選んで一括設定できます。この画面だけは「適用して指標一覧へ」を選ぶまで反映されません。「キャンセル」を選ぶと、変更は破棄されて指標一覧に戻ります。</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="12" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B161" s="13" t="inlineStr">
-        <is>
-          <t>入口 ｜ 操作 ｜ こんなときに</t>
-        </is>
-      </c>
-      <c r="C161" s="12" t="inlineStr"/>
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>作った組み合わせは「名前をつけて保存」するとマイテンプレートに登録されます。他の権限を設定するときに読み込めるので、同じ組み合わせを作り直す必要はありません。保存した組み合わせは更新・削除もできます。</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B162" s="4" t="inlineStr">
-        <is>
-          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
-        </is>
-      </c>
-      <c r="C162" s="4" t="inlineStr"/>
+      <c r="A162" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B162" s="11" t="inlineStr">
+        <is>
+          <t>作成した権限を修正する</t>
+        </is>
+      </c>
+      <c r="C162" s="10" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>権限一覧のマス目 ｜ 権限×画面のマス目を選択 ｜ 一覧で気づいた箇所をその場で直したいとき</t>
+          <t>作成済みの権限は、いくつかの入口から修正できます。どこから入っても同じ編集画面が開き、保存すると元いた画面に戻ります。</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B164" s="4" t="inlineStr">
-        <is>
-          <t>役割サマリ ｜ 対象の権限の行で「権限編集」 ｜ 全体を確認していて気づいたとき</t>
-        </is>
-      </c>
-      <c r="C164" s="4" t="inlineStr"/>
+      <c r="A164" s="12" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B164" s="13" t="inlineStr">
+        <is>
+          <t>入口 ｜ 操作 ｜ こんなときに</t>
+        </is>
+      </c>
+      <c r="C164" s="12" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -2768,7 +2784,7 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>割当編集 ｜ 権限の行で「権限編集 →」 ｜ メンバーの設定中に権限そのものを直したいとき（割当編集の開き方は「権限をメンバーに割り当てる」で説明します）</t>
+          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr"/>
@@ -2776,97 +2792,97 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
+          <t>権限一覧のマス目 ｜ 権限×画面のマス目を選択 ｜ 一覧で気づいた箇所をその場で直したいとき</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>役割サマリ ｜ 対象の権限の行で「権限編集」 ｜ 全体を確認していて気づいたとき</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>割当編集 ｜ 権限の行で「権限編集 →」 ｜ メンバーの設定中に権限そのものを直したいとき（割当編集の開き方は「権限をメンバーに割り当てる」で説明します）</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
           <t>権限名を変えるには — 編集画面の上部にある基本情報で、権限名を書き換えて「基本情報を更新」を選択します。権限名を変えても、その権限を割り当てた方の設定はそのまま引き継がれます。</t>
         </is>
       </c>
-      <c r="C166" s="4" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="15" t="inlineStr">
+      <c r="C169" s="4" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B167" s="15" t="inlineStr">
+      <c r="B170" s="15" t="inlineStr">
         <is>
           <t>【画像⑨】</t>
         </is>
       </c>
-      <c r="C167" s="15" t="inlineStr">
+      <c r="C170" s="15" t="inlineStr">
         <is>
           <t>マス目を選択して該当箇所へ移動したところ　※スクリーンショット未取得（撮影リスト ⑨ 番）</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="5" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B168" s="6" t="inlineStr">
+      <c r="B171" s="6" t="inlineStr">
         <is>
           <t>&gt; 権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
         </is>
       </c>
-      <c r="C168" s="5" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="5" t="inlineStr">
+      <c r="C171" s="5" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B169" s="6" t="inlineStr">
+      <c r="B172" s="6" t="inlineStr">
         <is>
           <t>&gt; 権限の修正は、その権限をお持ちの全員に反映されますのでご注意ください。特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
         </is>
       </c>
-      <c r="C169" s="5" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選ぶと、その場で権限を作れます。作成後は元の割当編集の画面に戻ります。</t>
-        </is>
-      </c>
-      <c r="C170" s="4" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B171" s="11" t="inlineStr">
-        <is>
-          <t>権限を変更・解除する</t>
-        </is>
-      </c>
-      <c r="C171" s="10" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B172" s="4" t="inlineStr">
-        <is>
-          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
-        </is>
-      </c>
-      <c r="C172" s="4" t="inlineStr"/>
+      <c r="C172" s="5" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -2876,49 +2892,53 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>異動や退職で、割り当て済みの権限を付け替える／外すときの操作です。</t>
+          <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選ぶと、その場で権限を作れます。作成後は元の割当編集の画面に戻ります。</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B174" s="9" t="inlineStr">
-        <is>
-          <t>別の権限に変更する</t>
-        </is>
-      </c>
-      <c r="C174" s="8" t="inlineStr"/>
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>権限を削除するには — 権限一覧の対象の行で「削除」を選択します。</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B175" s="4" t="inlineStr">
-        <is>
-          <t>割当編集の画面で、別の権限を選んで保存します。それまでの権限は自動的に外れます。 選択する前に、行に「選ぶと『◯◯』から置き換わります」と表示されます。保存するとユーザー割当に戻ります。</t>
-        </is>
-      </c>
-      <c r="C175" s="4" t="inlineStr"/>
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 使っている方がいる権限は削除できません</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t>その権限を割り当てている方が1名でもいる場合は、警告が出て削除できません。先に「ユーザー割当」でその方に別の権限を割り当てるか、割当を外してから削除してください。権限を消すとその方は何も見られなくなるためです。</t>
+        </is>
+      </c>
     </row>
     <row r="176">
-      <c r="A176" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B176" s="9" t="inlineStr">
-        <is>
-          <t>権限を外す</t>
-        </is>
-      </c>
-      <c r="C176" s="8" t="inlineStr"/>
+      <c r="A176" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B176" s="11" t="inlineStr">
+        <is>
+          <t>権限を変更・解除する</t>
+        </is>
+      </c>
+      <c r="C176" s="10" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -2928,36 +2948,36 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。保存するとユーザー割当に戻り、その方は「未割当」と表示されます。</t>
+          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B178" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 権限を外した方は、ログインしても画面が表示されませんのでご注意ください。退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
-        </is>
-      </c>
-      <c r="C178" s="5" t="inlineStr"/>
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>異動や退職で、割り当て済みの権限を付け替える／外すときの操作です。</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B179" s="11" t="inlineStr">
-        <is>
-          <t>オーナーだけができること</t>
-        </is>
-      </c>
-      <c r="C179" s="10" t="inlineStr"/>
+      <c r="A179" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B179" s="9" t="inlineStr">
+        <is>
+          <t>別の権限に変更する</t>
+        </is>
+      </c>
+      <c r="C179" s="8" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
@@ -2967,98 +2987,98 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
+          <t>割当編集の画面で、別の権限を選んで保存します。それまでの権限は自動的に外れます。 選択する前に、行に「選ぶと『◯◯』から置き換わります」と表示されます。保存するとユーザー割当に戻ります。</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="12" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B181" s="13" t="inlineStr">
-        <is>
-          <t>操作 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C181" s="12" t="inlineStr"/>
+      <c r="A181" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B181" s="9" t="inlineStr">
+        <is>
+          <t>権限を外す</t>
+        </is>
+      </c>
+      <c r="C181" s="8" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
+          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。保存するとユーザー割当に戻り、その方は「未割当」と表示されます。</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B183" s="4" t="inlineStr">
-        <is>
-          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
-        </is>
-      </c>
-      <c r="C183" s="4" t="inlineStr"/>
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 権限を外した方は、ログインしても画面が表示されませんのでご注意ください。退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B184" s="4" t="inlineStr">
-        <is>
-          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
-        </is>
-      </c>
-      <c r="C184" s="4" t="inlineStr"/>
+      <c r="A184" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B184" s="11" t="inlineStr">
+        <is>
+          <t>オーナーだけができること</t>
+        </is>
+      </c>
+      <c r="C184" s="10" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B185" s="11" t="inlineStr">
-        <is>
-          <t>設定内容を確認する</t>
-        </is>
-      </c>
-      <c r="C185" s="10" t="inlineStr"/>
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B186" s="4" t="inlineStr">
-        <is>
-          <t>設定が増えてきたら、一覧で確認できます。</t>
-        </is>
-      </c>
-      <c r="C186" s="4" t="inlineStr"/>
+      <c r="A186" s="12" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B186" s="13" t="inlineStr">
+        <is>
+          <t>操作 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C186" s="12" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
+          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr"/>
@@ -3066,32 +3086,28 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>役割サマリ — 権限ごとに「割当ユーザー ◯名」を確認できます。店舗が未設定の方がいる場合は警告が表示されます。</t>
+          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B189" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑩】</t>
-        </is>
-      </c>
-      <c r="C189" s="15" t="inlineStr">
-        <is>
-          <t>役割サマリの画面　※スクリーンショット未取得（撮影リスト ⑩ 番）</t>
-        </is>
-      </c>
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="10" t="inlineStr">
@@ -3101,23 +3117,23 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>ケース別のやり方</t>
+          <t>設定内容を確認する</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B191" s="17" t="inlineStr">
-        <is>
-          <t>どのケースも共通の登録手順</t>
-        </is>
-      </c>
-      <c r="C191" s="16" t="inlineStr"/>
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>設定が増えてきたら、一覧で確認できます。</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
@@ -3127,7 +3143,7 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>権限の登録は、どのケースでも次の3つを順に行います。</t>
+          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr"/>
@@ -3135,90 +3151,94 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>役割サマリ — 権限ごとに「割当ユーザー ◯名」を確認できます。店舗が未設定の方がいる場合は警告が表示されます。</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B194" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑩】</t>
+        </is>
+      </c>
+      <c r="C194" s="15" t="inlineStr">
+        <is>
+          <t>役割サマリの画面　※スクリーンショット未取得（撮影リスト ⑩ 番）</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B195" s="11" t="inlineStr">
+        <is>
+          <t>ケース別のやり方</t>
+        </is>
+      </c>
+      <c r="C195" s="10" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B196" s="17" t="inlineStr">
+        <is>
+          <t>どのケースも共通の登録手順</t>
+        </is>
+      </c>
+      <c r="C196" s="16" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>権限の登録は、どのケースでも次の3つを順に行います。</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B193" s="4" t="inlineStr">
+      <c r="B198" s="4" t="inlineStr">
         <is>
           <t>1. 権限を作成する — 雛形を選び、権限名と区分を決め、画面ごとに「操作／閲覧／なし」を設定して保存します。</t>
         </is>
       </c>
-      <c r="C193" s="4" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>2. 権限をメンバーに割り当てる — 対象の方に、作った権限を付けます。1人が持てる権限は1つです。</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B195" s="4" t="inlineStr">
-        <is>
-          <t>3. 担当店舗を設定する — 区分が「店舗」の場合のみ。どの店舗の数字を見せるかを、メンバーごとに選びます。</t>
-        </is>
-      </c>
-      <c r="C195" s="4" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B196" s="4" t="inlineStr">
-        <is>
-          <t>以下は、この3つのうちケースによって変わる部分だけをご案内します。</t>
-        </is>
-      </c>
-      <c r="C196" s="4" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B197" s="17" t="inlineStr">
-        <is>
-          <t>ケース別の設定</t>
-        </is>
-      </c>
-      <c r="C197" s="16" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B198" s="9" t="inlineStr">
-        <is>
-          <t>経理担当に、売上とお支払だけ見せたい</t>
-        </is>
-      </c>
-      <c r="C198" s="8" t="inlineStr"/>
+      <c r="C198" s="4" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>区分は「会社」、雛形は「本部管理」を選びます。従業員（閲覧）・従業員管理・ユーザーを「なし」にすると、売上や仕入の数字とお支払いは見えて、従業員の情報は見えない状態になります。区分が「会社」なので、担当店舗の設定は不要です。</t>
+          <t>2. 権限をメンバーに割り当てる — 対象の方に、作った権限を付けます。1人が持てる権限は1つです。</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr"/>
@@ -3226,41 +3246,41 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>ただしお支払いは会社の画面、費用設定・予算設定は店舗の画面です。経理の方が両方を扱う場合は、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当ててください。1人が持てる権限は1つのためです。</t>
+          <t>3. 担当店舗を設定する — 区分が「店舗」の場合のみ。どの店舗の数字を見せるかを、メンバーごとに選びます。</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B201" s="9" t="inlineStr">
-        <is>
-          <t>人事担当に、従業員情報だけ見せたい</t>
-        </is>
-      </c>
-      <c r="C201" s="8" t="inlineStr"/>
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>以下は、この3つのうちケースによって変わる部分だけをご案内します。</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B202" s="4" t="inlineStr">
-        <is>
-          <t>区分は「会社」、雛形は「本部管理」を選びます。売上分析・仕入分析・詳細分析・集計・お支払いを「なし」にすると、従業員の情報と締め管理は見えて、経営の数字は見えない状態になります。担当店舗の設定は不要です。</t>
-        </is>
-      </c>
-      <c r="C202" s="4" t="inlineStr"/>
+      <c r="A202" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B202" s="17" t="inlineStr">
+        <is>
+          <t>ケース別の設定</t>
+        </is>
+      </c>
+      <c r="C202" s="16" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="8" t="inlineStr">
@@ -3270,7 +3290,7 @@
       </c>
       <c r="B203" s="9" t="inlineStr">
         <is>
-          <t>アルバイトリーダーに、一部の画面だけ見せたい</t>
+          <t>経理担当に、売上とお支払だけ見せたい</t>
         </is>
       </c>
       <c r="C203" s="8" t="inlineStr"/>
@@ -3283,36 +3303,36 @@
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>区分は「店舗」、雛形は「店長」を選びます。仕入分析・詳細分析・従業員（閲覧）・従業員管理・締め管理・費用設定・予算設定を「なし」にすると、売上と日々の入力画面だけが残ります。所属する店舗を担当店舗に設定してください。</t>
+          <t>区分は「会社」、雛形は「本部管理」を選びます。従業員（閲覧）・従業員管理・ユーザーを「なし」にすると、売上や仕入の数字とお支払いは見えて、従業員の情報は見えない状態になります。区分が「会社」なので、担当店舗の設定は不要です。</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="8" t="inlineStr">
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>ただしお支払いは会社の画面、費用設定・予算設定は店舗の画面です。経理の方が両方を扱う場合は、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当ててください。1人が持てる権限は1つのためです。</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="8" t="inlineStr">
         <is>
           <t>小見出し</t>
         </is>
       </c>
-      <c r="B205" s="9" t="inlineStr">
-        <is>
-          <t>複数の店舗をまとめて見せたい（エリアマネージャー）</t>
-        </is>
-      </c>
-      <c r="C205" s="8" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B206" s="4" t="inlineStr">
-        <is>
-          <t>区分は「店舗」、雛形は「店長」を選びます。画面の設定は変えずに権限名を「エリアマネージャー」などに変え、担当店舗で複数の店舗を選びます。</t>
-        </is>
-      </c>
-      <c r="C206" s="4" t="inlineStr"/>
+      <c r="B206" s="9" t="inlineStr">
+        <is>
+          <t>人事担当に、従業員情報だけ見せたい</t>
+        </is>
+      </c>
+      <c r="C206" s="8" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -3322,7 +3342,7 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>エリアマネージャーは雛形の一覧にはありません。担当する店舗数や見せる範囲は組織によって変わるため、権限は「店長」と共通のものを使い、店舗はメンバーごとに設定する形にしています。</t>
+          <t>区分は「会社」、雛形は「本部管理」を選びます。売上分析・仕入分析・詳細分析・集計・お支払いを「なし」にすると、従業員の情報と締め管理は見えて、経営の数字は見えない状態になります。担当店舗の設定は不要です。</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr"/>
@@ -3335,7 +3355,7 @@
       </c>
       <c r="B208" s="9" t="inlineStr">
         <is>
-          <t>新しく入った方には、まず最小限から始めたい</t>
+          <t>アルバイトリーダーに、一部の画面だけ見せたい</t>
         </is>
       </c>
       <c r="C208" s="8" t="inlineStr"/>
@@ -3348,7 +3368,7 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>区分は「店舗」、雛形は「まっさら（なし）」を選びます。ダッシュボード以外をすべて「なし」にすると、ログインしてダッシュボードだけが見える状態になります。慣れてきたら、必要な画面を1つずつ追加してください。</t>
+          <t>区分は「店舗」、雛形は「店長」を選びます。仕入分析・詳細分析・従業員（閲覧）・従業員管理・締め管理・費用設定・予算設定を「なし」にすると、売上と日々の入力画面だけが残ります。所属する店舗を担当店舗に設定してください。</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr"/>
@@ -3361,7 +3381,7 @@
       </c>
       <c r="B210" s="9" t="inlineStr">
         <is>
-          <t>会社と店舗の両方の画面を使わせたい</t>
+          <t>複数の店舗をまとめて見せたい（エリアマネージャー）</t>
         </is>
       </c>
       <c r="C210" s="8" t="inlineStr"/>
@@ -3374,36 +3394,36 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>1つの権限ではできません。区分ごとに権限を2つ作り、担当を分けて割り当ててください。1人が持てる権限は1つのためです。</t>
+          <t>区分は「店舗」、雛形は「店長」を選びます。画面の設定は変えずに権限名を「エリアマネージャー」などに変え、担当店舗で複数の店舗を選びます。</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B212" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 画面の名前は区分によって変わります。会社の権限を作っているときに「費用設定」が見当たらないのは、それが店舗の画面のためです。どの画面がどちらに属するかは「権限を作成する」の STEP 3 にある図でご確認いただけます。</t>
-        </is>
-      </c>
-      <c r="C212" s="5" t="inlineStr"/>
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>エリアマネージャーは雛形の一覧にはありません。担当する店舗数や見せる範囲は組織によって変わるため、権限は「店長」と共通のものを使い、店舗はメンバーごとに設定する形にしています。</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B213" s="11" t="inlineStr">
-        <is>
-          <t>よくあるご質問</t>
-        </is>
-      </c>
-      <c r="C213" s="10" t="inlineStr"/>
+      <c r="A213" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B213" s="9" t="inlineStr">
+        <is>
+          <t>新しく入った方には、まず最小限から始めたい</t>
+        </is>
+      </c>
+      <c r="C213" s="8" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
@@ -3413,95 +3433,75 @@
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
+          <t>区分は「店舗」、雛形は「まっさら（なし）」を選びます。ダッシュボード以外をすべて「なし」にすると、ログインしてダッシュボードだけが見える状態になります。慣れてきたら、必要な画面を1つずつ追加してください。</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B215" s="9" t="inlineStr">
+        <is>
+          <t>会社と店舗の両方の画面を使わせたい</t>
+        </is>
+      </c>
+      <c r="C215" s="8" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>1つの権限ではできません。区分ごとに権限を2つ作り、担当を分けて割り当ててください。1人が持てる権限は1つのためです。</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 画面の名前は区分によって変わります。会社の権限を作っているときに「費用設定」が見当たらないのは、それが店舗の画面のためです。どの画面がどちらに属するかは「権限を作成する」の STEP 3 にある図でご確認いただけます。</t>
+        </is>
+      </c>
+      <c r="C217" s="5" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B218" s="11" t="inlineStr">
+        <is>
+          <t>よくあるご質問</t>
+        </is>
+      </c>
+      <c r="C218" s="10" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
           <t>権限の持ち方、見える範囲、設定を間違えたときの戻し方についてのご質問です。</t>
         </is>
       </c>
-      <c r="C214" s="4" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B215" s="18" t="inlineStr">
-        <is>
-          <t>Q. 1人に複数の権限を割り当てられますか？</t>
-        </is>
-      </c>
-      <c r="C215" s="18" t="inlineStr">
-        <is>
-          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B216" s="18" t="inlineStr">
-        <is>
-          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
-        </is>
-      </c>
-      <c r="C216" s="18" t="inlineStr">
-        <is>
-          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B217" s="18" t="inlineStr">
-        <is>
-          <t>Q. 権限を変更すると、誰に影響しますか？</t>
-        </is>
-      </c>
-      <c r="C217" s="18" t="inlineStr">
-        <is>
-          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B218" s="18" t="inlineStr">
-        <is>
-          <t>Q. 設定した権限はいつから反映されますか？</t>
-        </is>
-      </c>
-      <c r="C218" s="18" t="inlineStr">
-        <is>
-          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B219" s="18" t="inlineStr">
-        <is>
-          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
-        </is>
-      </c>
-      <c r="C219" s="18" t="inlineStr">
-        <is>
-          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
-        </is>
-      </c>
+      <c r="C219" s="4" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="18" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="B220" s="18" t="inlineStr">
         <is>
-          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
+          <t>Q. 1人に複数の権限を割り当てられますか？</t>
         </is>
       </c>
       <c r="C220" s="18" t="inlineStr">
         <is>
-          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
+          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
         </is>
       </c>
     </row>
@@ -3528,12 +3528,12 @@
       </c>
       <c r="B221" s="18" t="inlineStr">
         <is>
-          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
+          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
         </is>
       </c>
       <c r="C221" s="18" t="inlineStr">
         <is>
-          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
+          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3545,12 @@
       </c>
       <c r="B222" s="18" t="inlineStr">
         <is>
-          <t>Q. 役職を変更すると権限も変わりますか？</t>
+          <t>Q. 権限を変更すると、誰に影響しますか？</t>
         </is>
       </c>
       <c r="C222" s="18" t="inlineStr">
         <is>
-          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
+          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
         </is>
       </c>
     </row>
@@ -3562,12 +3562,12 @@
       </c>
       <c r="B223" s="18" t="inlineStr">
         <is>
-          <t>Q. 自分の権限を変更できますか？</t>
+          <t>Q. 設定した権限はいつから反映されますか？</t>
         </is>
       </c>
       <c r="C223" s="18" t="inlineStr">
         <is>
-          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
+          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="B224" s="18" t="inlineStr">
         <is>
-          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
+          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
         </is>
       </c>
       <c r="C224" s="18" t="inlineStr">
         <is>
-          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
+          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
         </is>
       </c>
     </row>
@@ -3596,12 +3596,12 @@
       </c>
       <c r="B225" s="18" t="inlineStr">
         <is>
-          <t>Q. 権限が未設定の方はどうなりますか？</t>
+          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
         </is>
       </c>
       <c r="C225" s="18" t="inlineStr">
         <is>
-          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
+          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
         </is>
       </c>
     </row>
@@ -3613,118 +3613,138 @@
       </c>
       <c r="B226" s="18" t="inlineStr">
         <is>
+          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
+        </is>
+      </c>
+      <c r="C226" s="18" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B227" s="18" t="inlineStr">
+        <is>
+          <t>Q. 役職を変更すると権限も変わりますか？</t>
+        </is>
+      </c>
+      <c r="C227" s="18" t="inlineStr">
+        <is>
+          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B228" s="18" t="inlineStr">
+        <is>
+          <t>Q. 自分の権限を変更できますか？</t>
+        </is>
+      </c>
+      <c r="C228" s="18" t="inlineStr">
+        <is>
+          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B229" s="18" t="inlineStr">
+        <is>
+          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
+        </is>
+      </c>
+      <c r="C229" s="18" t="inlineStr">
+        <is>
+          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B230" s="18" t="inlineStr">
+        <is>
+          <t>Q. 権限が未設定の方はどうなりますか？</t>
+        </is>
+      </c>
+      <c r="C230" s="18" t="inlineStr">
+        <is>
+          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B231" s="18" t="inlineStr">
+        <is>
           <t>Q. 新しい画面が追加された場合、権限はどうなりますか？</t>
         </is>
       </c>
-      <c r="C226" s="18" t="inlineStr">
+      <c r="C231" s="18" t="inlineStr">
         <is>
           <t>すべての権限で「なし」の状態で追加されます。ご利用になる場合は、権限設定から個別に許可してください。</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="10" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B227" s="11" t="inlineStr">
+      <c r="B232" s="11" t="inlineStr">
         <is>
           <t>用語の説明</t>
         </is>
       </c>
-      <c r="C227" s="10" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B228" s="4" t="inlineStr">
-        <is>
-          <t>画面に出てくる言葉の意味です。読んでいて分からない言葉が出たときにご覧ください。</t>
-        </is>
-      </c>
-      <c r="C228" s="4" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="12" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B229" s="13" t="inlineStr">
-        <is>
-          <t>用語 ｜ 意味</t>
-        </is>
-      </c>
-      <c r="C229" s="12" t="inlineStr"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B230" s="4" t="inlineStr">
-        <is>
-          <t>権限 ｜ 「どの画面をどこまで使えるか」を決めたもの。名前を付けて保存します</t>
-        </is>
-      </c>
-      <c r="C230" s="4" t="inlineStr"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B231" s="4" t="inlineStr">
-        <is>
-          <t>区分 ｜ その権限が会社画面向けか店舗画面向けか。会社／店舗のどちらかを選びます</t>
-        </is>
-      </c>
-      <c r="C231" s="4" t="inlineStr"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B232" s="4" t="inlineStr">
-        <is>
-          <t>担当店舗 ｜ 店舗の権限を持つメンバーが、どの店舗を担当するか。メンバーごとに設定します</t>
-        </is>
-      </c>
-      <c r="C232" s="4" t="inlineStr"/>
+      <c r="C232" s="10" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>スコープ選択 ｜ 画面上部にある、会社と店舗を切り替える欄。ここで選んだ側の権限と画面が表示されます</t>
+          <t>画面に出てくる言葉の意味です。読んでいて分からない言葉が出たときにご覧ください。</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B234" s="4" t="inlineStr">
-        <is>
-          <t>雛形（ベース） ｜ 権限を作るときの土台。近いものを選んで違うところだけ直します</t>
-        </is>
-      </c>
-      <c r="C234" s="4" t="inlineStr"/>
+      <c r="A234" s="12" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B234" s="13" t="inlineStr">
+        <is>
+          <t>用語 ｜ 意味</t>
+        </is>
+      </c>
+      <c r="C234" s="12" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
@@ -3734,7 +3754,7 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>権限母体 ｜ 経理・人事など複数の権限を派生させるための、共通の土台となる権限</t>
+          <t>権限 ｜ 「どの画面をどこまで使えるか」を決めたもの。名前を付けて保存します</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr"/>
@@ -3747,7 +3767,7 @@
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>権限一覧 ｜ 作った権限を、画面ごとの設定とあわせて一覧で見比べる画面</t>
+          <t>区分 ｜ その権限が会社画面向けか店舗画面向けか。会社／店舗のどちらかを選びます</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr"/>
@@ -3760,7 +3780,7 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>役割サマリ ｜ 権限ごとに、何名に割り当てているかを確認する画面</t>
+          <t>担当店舗 ｜ 店舗の権限を持つメンバーが、どの店舗を担当するか。メンバーごとに設定します</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr"/>
@@ -3773,7 +3793,7 @@
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>指標 ｜ 売上・原価・人件費など、画面に表示される数字のこと</t>
+          <t>スコープ選択 ｜ 画面上部にある、会社と店舗を切り替える欄。ここで選んだ側の権限と画面が表示されます</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr"/>
@@ -3781,38 +3801,38 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>「役職」は従業員情報に登録された肩書きで、権限とは別のものです。役職を変更しても権限は変わりません。</t>
+          <t>雛形（ベース） ｜ 権限を作るときの土台。近いものを選んで違うところだけ直します</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B240" s="11" t="inlineStr">
-        <is>
-          <t>参照リンク</t>
-        </is>
-      </c>
-      <c r="C240" s="10" t="inlineStr"/>
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="inlineStr">
+        <is>
+          <t>権限母体 ｜ 経理・人事など複数の権限を派生させるための、共通の土台となる権限</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>箇条書き</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>・[ラクミー経営管理 ログイン](https://manager.rakmy.jp/users/sign_in)</t>
+          <t>権限一覧 ｜ 作った権限を、画面ごとの設定とあわせて一覧で見比べる画面</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr"/>
@@ -3820,12 +3840,12 @@
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>箇条書き</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>・[店舗の登録方法](https://help.rakmy.jp/management/店舗)</t>
+          <t>役割サマリ ｜ 権限ごとに、何名に割り当てているかを確認する画面</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr"/>
@@ -3833,18 +3853,83 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
+          <t>指標 ｜ 売上・原価・人件費など、画面に表示される数字のこと</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>「役職」は従業員情報に登録された肩書きで、権限とは別のものです。役職を変更しても権限は変わりません。</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B245" s="11" t="inlineStr">
+        <is>
+          <t>参照リンク</t>
+        </is>
+      </c>
+      <c r="C245" s="10" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>箇条書き</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>・[ラクミー経営管理 ログイン](https://manager.rakmy.jp/users/sign_in)</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="4" t="inlineStr">
+        <is>
+          <t>箇条書き</t>
+        </is>
+      </c>
+      <c r="B247" s="4" t="inlineStr">
+        <is>
+          <t>・[店舗の登録方法](https://help.rakmy.jp/management/店舗)</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
           <t>サポートが必要ですか？ [サポートチームに連絡](https://docs.google.com/forms/d/e/1FAIpQLSe1qwnma82vLEpQQNdzjl_gLSt_qHMHZp6eqmhaziUB11IAOA/viewform)</t>
         </is>
       </c>
-      <c r="C243" s="4" t="inlineStr"/>
+      <c r="C248" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C243"/>
+  <autoFilter ref="A2:C248"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/20260806_権限設定_ヘルプページ.xlsx
+++ b/20260806_権限設定_ヘルプページ.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ヘルプページ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$248</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$253</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C248"/>
+  <dimension ref="A1:C253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2836,53 +2836,49 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>権限名を変えるには — 編集画面の上部にある基本情報で、権限名を書き換えて「基本情報を更新」を選択します。権限名を変えても、その権限を割り当てた方の設定はそのまま引き継がれます。</t>
+          <t>権限名を変えるには — 編集画面の上部にある基本情報で、権限名を書き換えて保存します。名前を変えて保存すると、2つのどちらにするかを選べます。</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B170" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑨】</t>
-        </is>
-      </c>
-      <c r="C170" s="15" t="inlineStr">
-        <is>
-          <t>マス目を選択して該当箇所へ移動したところ　※スクリーンショット未取得（撮影リスト ⑨ 番）</t>
-        </is>
-      </c>
+      <c r="A170" s="12" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B170" s="13" t="inlineStr">
+        <is>
+          <t>選ぶもの ｜ どうなるか</t>
+        </is>
+      </c>
+      <c r="C170" s="12" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B171" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
-        </is>
-      </c>
-      <c r="C171" s="5" t="inlineStr"/>
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>上書きする ｜ この権限の名前が変わります。割り当てている方はそのまま新しい名前の権限を持ちます。元の名前の権限は残りません</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B172" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 権限の修正は、その権限をお持ちの全員に反映されますのでご注意ください。特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
-        </is>
-      </c>
-      <c r="C172" s="5" t="inlineStr"/>
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>新しい権限として保存 ｜ 元の権限はそのまま残り、新しい名前の権限が追加されます。割り当ては元の権限のままです</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -2892,66 +2888,70 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選ぶと、その場で権限を作れます。作成後は元の割当編集の画面に戻ります。</t>
+          <t>似た権限をもう1つ作りたいときは「新しい権限として保存」を選んでください。たとえば「エリア長」を土台に「西エリア長」を作りたい場合です。</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B174" s="4" t="inlineStr">
-        <is>
-          <t>権限を削除するには — 権限一覧の対象の行で「削除」を選択します。</t>
-        </is>
-      </c>
-      <c r="C174" s="4" t="inlineStr"/>
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 名前を変えないで保存したときは選択は出ません</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>画面ごとの設定だけを直した場合は、そのまま上書きされます。その権限を割り当てている全員に反映されます。</t>
+        </is>
+      </c>
     </row>
     <row r="175">
-      <c r="A175" s="5" t="inlineStr">
+      <c r="A175" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B175" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑨】</t>
+        </is>
+      </c>
+      <c r="C175" s="15" t="inlineStr">
+        <is>
+          <t>マス目を選択して該当箇所へ移動したところ　※スクリーンショット未取得（撮影リスト ⑨ 番）</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B175" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 使っている方がいる権限は削除できません</t>
-        </is>
-      </c>
-      <c r="C175" s="5" t="inlineStr">
-        <is>
-          <t>その権限を割り当てている方が1名でもいる場合は、警告が出て削除できません。先に「ユーザー割当」でその方に別の権限を割り当てるか、割当を外してから削除してください。権限を消すとその方は何も見られなくなるためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B176" s="11" t="inlineStr">
-        <is>
-          <t>権限を変更・解除する</t>
-        </is>
-      </c>
-      <c r="C176" s="10" t="inlineStr"/>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B177" s="4" t="inlineStr">
-        <is>
-          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
-        </is>
-      </c>
-      <c r="C177" s="4" t="inlineStr"/>
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B177" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 権限の修正は、その権限をお持ちの全員に反映されますのでご注意ください。特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
@@ -2961,49 +2961,53 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>異動や退職で、割り当て済みの権限を付け替える／外すときの操作です。</t>
+          <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選ぶと、その場で権限を作れます。作成後は元の割当編集の画面に戻ります。</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B179" s="9" t="inlineStr">
-        <is>
-          <t>別の権限に変更する</t>
-        </is>
-      </c>
-      <c r="C179" s="8" t="inlineStr"/>
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>権限を削除するには — 権限一覧の対象の行で「削除」を選択します。</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B180" s="4" t="inlineStr">
-        <is>
-          <t>割当編集の画面で、別の権限を選んで保存します。それまでの権限は自動的に外れます。 選択する前に、行に「選ぶと『◯◯』から置き換わります」と表示されます。保存するとユーザー割当に戻ります。</t>
-        </is>
-      </c>
-      <c r="C180" s="4" t="inlineStr"/>
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 使っている方がいる権限は削除できません</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>その権限を割り当てている方が1名でもいる場合は、警告が出て削除できません。先に「ユーザー割当」でその方に別の権限を割り当てるか、割当を外してから削除してください。権限を消すとその方は何も見られなくなるためです。</t>
+        </is>
+      </c>
     </row>
     <row r="181">
-      <c r="A181" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B181" s="9" t="inlineStr">
-        <is>
-          <t>権限を外す</t>
-        </is>
-      </c>
-      <c r="C181" s="8" t="inlineStr"/>
+      <c r="A181" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B181" s="11" t="inlineStr">
+        <is>
+          <t>権限を変更・解除する</t>
+        </is>
+      </c>
+      <c r="C181" s="10" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -3013,36 +3017,36 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。保存するとユーザー割当に戻り、その方は「未割当」と表示されます。</t>
+          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B183" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 権限を外した方は、ログインしても画面が表示されませんのでご注意ください。退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
-        </is>
-      </c>
-      <c r="C183" s="5" t="inlineStr"/>
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>異動や退職で、割り当て済みの権限を付け替える／外すときの操作です。</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B184" s="11" t="inlineStr">
-        <is>
-          <t>オーナーだけができること</t>
-        </is>
-      </c>
-      <c r="C184" s="10" t="inlineStr"/>
+      <c r="A184" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B184" s="9" t="inlineStr">
+        <is>
+          <t>別の権限に変更する</t>
+        </is>
+      </c>
+      <c r="C184" s="8" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
@@ -3052,98 +3056,98 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
+          <t>割当編集の画面で、別の権限を選んで保存します。それまでの権限は自動的に外れます。 選択する前に、行に「選ぶと『◯◯』から置き換わります」と表示されます。保存するとユーザー割当に戻ります。</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="12" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B186" s="13" t="inlineStr">
-        <is>
-          <t>操作 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C186" s="12" t="inlineStr"/>
+      <c r="A186" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B186" s="9" t="inlineStr">
+        <is>
+          <t>権限を外す</t>
+        </is>
+      </c>
+      <c r="C186" s="8" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
+          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。保存するとユーザー割当に戻り、その方は「未割当」と表示されます。</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B188" s="4" t="inlineStr">
-        <is>
-          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
-        </is>
-      </c>
-      <c r="C188" s="4" t="inlineStr"/>
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 権限を外した方は、ログインしても画面が表示されませんのでご注意ください。退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B189" s="4" t="inlineStr">
-        <is>
-          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
-        </is>
-      </c>
-      <c r="C189" s="4" t="inlineStr"/>
+      <c r="A189" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B189" s="11" t="inlineStr">
+        <is>
+          <t>オーナーだけができること</t>
+        </is>
+      </c>
+      <c r="C189" s="10" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B190" s="11" t="inlineStr">
-        <is>
-          <t>設定内容を確認する</t>
-        </is>
-      </c>
-      <c r="C190" s="10" t="inlineStr"/>
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B191" s="4" t="inlineStr">
-        <is>
-          <t>設定が増えてきたら、一覧で確認できます。</t>
-        </is>
-      </c>
-      <c r="C191" s="4" t="inlineStr"/>
+      <c r="A191" s="12" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B191" s="13" t="inlineStr">
+        <is>
+          <t>操作 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C191" s="12" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
+          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr"/>
@@ -3151,32 +3155,28 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>役割サマリ — 権限ごとに「割当ユーザー ◯名」を確認できます。店舗が未設定の方がいる場合は警告が表示されます。</t>
+          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B194" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑩】</t>
-        </is>
-      </c>
-      <c r="C194" s="15" t="inlineStr">
-        <is>
-          <t>役割サマリの画面　※スクリーンショット未取得（撮影リスト ⑩ 番）</t>
-        </is>
-      </c>
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="10" t="inlineStr">
@@ -3186,23 +3186,23 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>ケース別のやり方</t>
+          <t>設定内容を確認する</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B196" s="17" t="inlineStr">
-        <is>
-          <t>どのケースも共通の登録手順</t>
-        </is>
-      </c>
-      <c r="C196" s="16" t="inlineStr"/>
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>設定が増えてきたら、一覧で確認できます。</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>権限の登録は、どのケースでも次の3つを順に行います。</t>
+          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr"/>
@@ -3220,90 +3220,94 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>役割サマリ — 権限ごとに「割当ユーザー ◯名」を確認できます。店舗が未設定の方がいる場合は警告が表示されます。</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B199" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑩】</t>
+        </is>
+      </c>
+      <c r="C199" s="15" t="inlineStr">
+        <is>
+          <t>役割サマリの画面　※スクリーンショット未取得（撮影リスト ⑩ 番）</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B200" s="11" t="inlineStr">
+        <is>
+          <t>ケース別のやり方</t>
+        </is>
+      </c>
+      <c r="C200" s="10" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B201" s="17" t="inlineStr">
+        <is>
+          <t>どのケースも共通の登録手順</t>
+        </is>
+      </c>
+      <c r="C201" s="16" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>権限の登録は、どのケースでも次の3つを順に行います。</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="inlineStr">
+        <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B198" s="4" t="inlineStr">
+      <c r="B203" s="4" t="inlineStr">
         <is>
           <t>1. 権限を作成する — 雛形を選び、権限名と区分を決め、画面ごとに「操作／閲覧／なし」を設定して保存します。</t>
         </is>
       </c>
-      <c r="C198" s="4" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B199" s="4" t="inlineStr">
-        <is>
-          <t>2. 権限をメンバーに割り当てる — 対象の方に、作った権限を付けます。1人が持てる権限は1つです。</t>
-        </is>
-      </c>
-      <c r="C199" s="4" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B200" s="4" t="inlineStr">
-        <is>
-          <t>3. 担当店舗を設定する — 区分が「店舗」の場合のみ。どの店舗の数字を見せるかを、メンバーごとに選びます。</t>
-        </is>
-      </c>
-      <c r="C200" s="4" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B201" s="4" t="inlineStr">
-        <is>
-          <t>以下は、この3つのうちケースによって変わる部分だけをご案内します。</t>
-        </is>
-      </c>
-      <c r="C201" s="4" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B202" s="17" t="inlineStr">
-        <is>
-          <t>ケース別の設定</t>
-        </is>
-      </c>
-      <c r="C202" s="16" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B203" s="9" t="inlineStr">
-        <is>
-          <t>経理担当に、売上とお支払だけ見せたい</t>
-        </is>
-      </c>
-      <c r="C203" s="8" t="inlineStr"/>
+      <c r="C203" s="4" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>区分は「会社」、雛形は「本部管理」を選びます。従業員（閲覧）・従業員管理・ユーザーを「なし」にすると、売上や仕入の数字とお支払いは見えて、従業員の情報は見えない状態になります。区分が「会社」なので、担当店舗の設定は不要です。</t>
+          <t>2. 権限をメンバーに割り当てる — 対象の方に、作った権限を付けます。1人が持てる権限は1つです。</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr"/>
@@ -3311,41 +3315,41 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>ただしお支払いは会社の画面、費用設定・予算設定は店舗の画面です。経理の方が両方を扱う場合は、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当ててください。1人が持てる権限は1つのためです。</t>
+          <t>3. 担当店舗を設定する — 区分が「店舗」の場合のみ。どの店舗の数字を見せるかを、メンバーごとに選びます。</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B206" s="9" t="inlineStr">
-        <is>
-          <t>人事担当に、従業員情報だけ見せたい</t>
-        </is>
-      </c>
-      <c r="C206" s="8" t="inlineStr"/>
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>以下は、この3つのうちケースによって変わる部分だけをご案内します。</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B207" s="4" t="inlineStr">
-        <is>
-          <t>区分は「会社」、雛形は「本部管理」を選びます。売上分析・仕入分析・詳細分析・集計・お支払いを「なし」にすると、従業員の情報と締め管理は見えて、経営の数字は見えない状態になります。担当店舗の設定は不要です。</t>
-        </is>
-      </c>
-      <c r="C207" s="4" t="inlineStr"/>
+      <c r="A207" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B207" s="17" t="inlineStr">
+        <is>
+          <t>ケース別の設定</t>
+        </is>
+      </c>
+      <c r="C207" s="16" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="8" t="inlineStr">
@@ -3355,7 +3359,7 @@
       </c>
       <c r="B208" s="9" t="inlineStr">
         <is>
-          <t>アルバイトリーダーに、一部の画面だけ見せたい</t>
+          <t>経理担当に、売上とお支払だけ見せたい</t>
         </is>
       </c>
       <c r="C208" s="8" t="inlineStr"/>
@@ -3368,36 +3372,36 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>区分は「店舗」、雛形は「店長」を選びます。仕入分析・詳細分析・従業員（閲覧）・従業員管理・締め管理・費用設定・予算設定を「なし」にすると、売上と日々の入力画面だけが残ります。所属する店舗を担当店舗に設定してください。</t>
+          <t>区分は「会社」、雛形は「本部管理」を選びます。従業員（閲覧）・従業員管理・ユーザーを「なし」にすると、売上や仕入の数字とお支払いは見えて、従業員の情報は見えない状態になります。区分が「会社」なので、担当店舗の設定は不要です。</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="8" t="inlineStr">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>ただしお支払いは会社の画面、費用設定・予算設定は店舗の画面です。経理の方が両方を扱う場合は、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当ててください。1人が持てる権限は1つのためです。</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="8" t="inlineStr">
         <is>
           <t>小見出し</t>
         </is>
       </c>
-      <c r="B210" s="9" t="inlineStr">
-        <is>
-          <t>複数の店舗をまとめて見せたい（エリアマネージャー）</t>
-        </is>
-      </c>
-      <c r="C210" s="8" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B211" s="4" t="inlineStr">
-        <is>
-          <t>区分は「店舗」、雛形は「店長」を選びます。画面の設定は変えずに権限名を「エリアマネージャー」などに変え、担当店舗で複数の店舗を選びます。</t>
-        </is>
-      </c>
-      <c r="C211" s="4" t="inlineStr"/>
+      <c r="B211" s="9" t="inlineStr">
+        <is>
+          <t>人事担当に、従業員情報だけ見せたい</t>
+        </is>
+      </c>
+      <c r="C211" s="8" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
@@ -3407,7 +3411,7 @@
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>エリアマネージャーは雛形の一覧にはありません。担当する店舗数や見せる範囲は組織によって変わるため、権限は「店長」と共通のものを使い、店舗はメンバーごとに設定する形にしています。</t>
+          <t>区分は「会社」、雛形は「本部管理」を選びます。売上分析・仕入分析・詳細分析・集計・お支払いを「なし」にすると、従業員の情報と締め管理は見えて、経営の数字は見えない状態になります。担当店舗の設定は不要です。</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr"/>
@@ -3420,7 +3424,7 @@
       </c>
       <c r="B213" s="9" t="inlineStr">
         <is>
-          <t>新しく入った方には、まず最小限から始めたい</t>
+          <t>アルバイトリーダーに、一部の画面だけ見せたい</t>
         </is>
       </c>
       <c r="C213" s="8" t="inlineStr"/>
@@ -3433,7 +3437,7 @@
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>区分は「店舗」、雛形は「まっさら（なし）」を選びます。ダッシュボード以外をすべて「なし」にすると、ログインしてダッシュボードだけが見える状態になります。慣れてきたら、必要な画面を1つずつ追加してください。</t>
+          <t>区分は「店舗」、雛形は「店長」を選びます。仕入分析・詳細分析・従業員（閲覧）・従業員管理・締め管理・費用設定・予算設定を「なし」にすると、売上と日々の入力画面だけが残ります。所属する店舗を担当店舗に設定してください。</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr"/>
@@ -3446,7 +3450,7 @@
       </c>
       <c r="B215" s="9" t="inlineStr">
         <is>
-          <t>会社と店舗の両方の画面を使わせたい</t>
+          <t>複数の店舗をまとめて見せたい（エリアマネージャー）</t>
         </is>
       </c>
       <c r="C215" s="8" t="inlineStr"/>
@@ -3459,36 +3463,36 @@
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>1つの権限ではできません。区分ごとに権限を2つ作り、担当を分けて割り当ててください。1人が持てる権限は1つのためです。</t>
+          <t>区分は「店舗」、雛形は「店長」を選びます。画面の設定は変えずに権限名を「エリアマネージャー」などに変え、担当店舗で複数の店舗を選びます。</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B217" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 画面の名前は区分によって変わります。会社の権限を作っているときに「費用設定」が見当たらないのは、それが店舗の画面のためです。どの画面がどちらに属するかは「権限を作成する」の STEP 3 にある図でご確認いただけます。</t>
-        </is>
-      </c>
-      <c r="C217" s="5" t="inlineStr"/>
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>エリアマネージャーは雛形の一覧にはありません。担当する店舗数や見せる範囲は組織によって変わるため、権限は「店長」と共通のものを使い、店舗はメンバーごとに設定する形にしています。</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B218" s="11" t="inlineStr">
-        <is>
-          <t>よくあるご質問</t>
-        </is>
-      </c>
-      <c r="C218" s="10" t="inlineStr"/>
+      <c r="A218" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B218" s="9" t="inlineStr">
+        <is>
+          <t>新しく入った方には、まず最小限から始めたい</t>
+        </is>
+      </c>
+      <c r="C218" s="8" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
@@ -3498,95 +3502,75 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
+          <t>区分は「店舗」、雛形は「まっさら（なし）」を選びます。ダッシュボード以外をすべて「なし」にすると、ログインしてダッシュボードだけが見える状態になります。慣れてきたら、必要な画面を1つずつ追加してください。</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B220" s="9" t="inlineStr">
+        <is>
+          <t>会社と店舗の両方の画面を使わせたい</t>
+        </is>
+      </c>
+      <c r="C220" s="8" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>1つの権限ではできません。区分ごとに権限を2つ作り、担当を分けて割り当ててください。1人が持てる権限は1つのためです。</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B222" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 画面の名前は区分によって変わります。会社の権限を作っているときに「費用設定」が見当たらないのは、それが店舗の画面のためです。どの画面がどちらに属するかは「権限を作成する」の STEP 3 にある図でご確認いただけます。</t>
+        </is>
+      </c>
+      <c r="C222" s="5" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B223" s="11" t="inlineStr">
+        <is>
+          <t>よくあるご質問</t>
+        </is>
+      </c>
+      <c r="C223" s="10" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
           <t>権限の持ち方、見える範囲、設定を間違えたときの戻し方についてのご質問です。</t>
         </is>
       </c>
-      <c r="C219" s="4" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B220" s="18" t="inlineStr">
-        <is>
-          <t>Q. 1人に複数の権限を割り当てられますか？</t>
-        </is>
-      </c>
-      <c r="C220" s="18" t="inlineStr">
-        <is>
-          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B221" s="18" t="inlineStr">
-        <is>
-          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
-        </is>
-      </c>
-      <c r="C221" s="18" t="inlineStr">
-        <is>
-          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B222" s="18" t="inlineStr">
-        <is>
-          <t>Q. 権限を変更すると、誰に影響しますか？</t>
-        </is>
-      </c>
-      <c r="C222" s="18" t="inlineStr">
-        <is>
-          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B223" s="18" t="inlineStr">
-        <is>
-          <t>Q. 設定した権限はいつから反映されますか？</t>
-        </is>
-      </c>
-      <c r="C223" s="18" t="inlineStr">
-        <is>
-          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B224" s="18" t="inlineStr">
-        <is>
-          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
-        </is>
-      </c>
-      <c r="C224" s="18" t="inlineStr">
-        <is>
-          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
-        </is>
-      </c>
+      <c r="C224" s="4" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="18" t="inlineStr">
@@ -3596,12 +3580,12 @@
       </c>
       <c r="B225" s="18" t="inlineStr">
         <is>
-          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
+          <t>Q. 1人に複数の権限を割り当てられますか？</t>
         </is>
       </c>
       <c r="C225" s="18" t="inlineStr">
         <is>
-          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
+          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
         </is>
       </c>
     </row>
@@ -3613,12 +3597,12 @@
       </c>
       <c r="B226" s="18" t="inlineStr">
         <is>
-          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
+          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
         </is>
       </c>
       <c r="C226" s="18" t="inlineStr">
         <is>
-          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
+          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
         </is>
       </c>
     </row>
@@ -3630,12 +3614,12 @@
       </c>
       <c r="B227" s="18" t="inlineStr">
         <is>
-          <t>Q. 役職を変更すると権限も変わりますか？</t>
+          <t>Q. 権限を変更すると、誰に影響しますか？</t>
         </is>
       </c>
       <c r="C227" s="18" t="inlineStr">
         <is>
-          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
+          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
         </is>
       </c>
     </row>
@@ -3647,12 +3631,12 @@
       </c>
       <c r="B228" s="18" t="inlineStr">
         <is>
-          <t>Q. 自分の権限を変更できますか？</t>
+          <t>Q. 設定した権限はいつから反映されますか？</t>
         </is>
       </c>
       <c r="C228" s="18" t="inlineStr">
         <is>
-          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
+          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
         </is>
       </c>
     </row>
@@ -3664,12 +3648,12 @@
       </c>
       <c r="B229" s="18" t="inlineStr">
         <is>
-          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
+          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
         </is>
       </c>
       <c r="C229" s="18" t="inlineStr">
         <is>
-          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
+          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
         </is>
       </c>
     </row>
@@ -3681,12 +3665,12 @@
       </c>
       <c r="B230" s="18" t="inlineStr">
         <is>
-          <t>Q. 権限が未設定の方はどうなりますか？</t>
+          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
         </is>
       </c>
       <c r="C230" s="18" t="inlineStr">
         <is>
-          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
+          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
         </is>
       </c>
     </row>
@@ -3698,118 +3682,138 @@
       </c>
       <c r="B231" s="18" t="inlineStr">
         <is>
+          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
+        </is>
+      </c>
+      <c r="C231" s="18" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B232" s="18" t="inlineStr">
+        <is>
+          <t>Q. 役職を変更すると権限も変わりますか？</t>
+        </is>
+      </c>
+      <c r="C232" s="18" t="inlineStr">
+        <is>
+          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B233" s="18" t="inlineStr">
+        <is>
+          <t>Q. 自分の権限を変更できますか？</t>
+        </is>
+      </c>
+      <c r="C233" s="18" t="inlineStr">
+        <is>
+          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B234" s="18" t="inlineStr">
+        <is>
+          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
+        </is>
+      </c>
+      <c r="C234" s="18" t="inlineStr">
+        <is>
+          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B235" s="18" t="inlineStr">
+        <is>
+          <t>Q. 権限が未設定の方はどうなりますか？</t>
+        </is>
+      </c>
+      <c r="C235" s="18" t="inlineStr">
+        <is>
+          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B236" s="18" t="inlineStr">
+        <is>
           <t>Q. 新しい画面が追加された場合、権限はどうなりますか？</t>
         </is>
       </c>
-      <c r="C231" s="18" t="inlineStr">
+      <c r="C236" s="18" t="inlineStr">
         <is>
           <t>すべての権限で「なし」の状態で追加されます。ご利用になる場合は、権限設定から個別に許可してください。</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="10" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B232" s="11" t="inlineStr">
+      <c r="B237" s="11" t="inlineStr">
         <is>
           <t>用語の説明</t>
         </is>
       </c>
-      <c r="C232" s="10" t="inlineStr"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B233" s="4" t="inlineStr">
-        <is>
-          <t>画面に出てくる言葉の意味です。読んでいて分からない言葉が出たときにご覧ください。</t>
-        </is>
-      </c>
-      <c r="C233" s="4" t="inlineStr"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="12" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B234" s="13" t="inlineStr">
-        <is>
-          <t>用語 ｜ 意味</t>
-        </is>
-      </c>
-      <c r="C234" s="12" t="inlineStr"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B235" s="4" t="inlineStr">
-        <is>
-          <t>権限 ｜ 「どの画面をどこまで使えるか」を決めたもの。名前を付けて保存します</t>
-        </is>
-      </c>
-      <c r="C235" s="4" t="inlineStr"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B236" s="4" t="inlineStr">
-        <is>
-          <t>区分 ｜ その権限が会社画面向けか店舗画面向けか。会社／店舗のどちらかを選びます</t>
-        </is>
-      </c>
-      <c r="C236" s="4" t="inlineStr"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B237" s="4" t="inlineStr">
-        <is>
-          <t>担当店舗 ｜ 店舗の権限を持つメンバーが、どの店舗を担当するか。メンバーごとに設定します</t>
-        </is>
-      </c>
-      <c r="C237" s="4" t="inlineStr"/>
+      <c r="C237" s="10" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>スコープ選択 ｜ 画面上部にある、会社と店舗を切り替える欄。ここで選んだ側の権限と画面が表示されます</t>
+          <t>画面に出てくる言葉の意味です。読んでいて分からない言葉が出たときにご覧ください。</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B239" s="4" t="inlineStr">
-        <is>
-          <t>雛形（ベース） ｜ 権限を作るときの土台。近いものを選んで違うところだけ直します</t>
-        </is>
-      </c>
-      <c r="C239" s="4" t="inlineStr"/>
+      <c r="A239" s="12" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B239" s="13" t="inlineStr">
+        <is>
+          <t>用語 ｜ 意味</t>
+        </is>
+      </c>
+      <c r="C239" s="12" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
@@ -3819,7 +3823,7 @@
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>権限母体 ｜ 経理・人事など複数の権限を派生させるための、共通の土台となる権限</t>
+          <t>権限 ｜ 「どの画面をどこまで使えるか」を決めたもの。名前を付けて保存します</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr"/>
@@ -3832,7 +3836,7 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>権限一覧 ｜ 作った権限を、画面ごとの設定とあわせて一覧で見比べる画面</t>
+          <t>区分 ｜ その権限が会社画面向けか店舗画面向けか。会社／店舗のどちらかを選びます</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr"/>
@@ -3845,7 +3849,7 @@
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>役割サマリ ｜ 権限ごとに、何名に割り当てているかを確認する画面</t>
+          <t>担当店舗 ｜ 店舗の権限を持つメンバーが、どの店舗を担当するか。メンバーごとに設定します</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr"/>
@@ -3858,7 +3862,7 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>指標 ｜ 売上・原価・人件費など、画面に表示される数字のこと</t>
+          <t>スコープ選択 ｜ 画面上部にある、会社と店舗を切り替える欄。ここで選んだ側の権限と画面が表示されます</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr"/>
@@ -3866,38 +3870,38 @@
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>「役職」は従業員情報に登録された肩書きで、権限とは別のものです。役職を変更しても権限は変わりません。</t>
+          <t>雛形（ベース） ｜ 権限を作るときの土台。近いものを選んで違うところだけ直します</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B245" s="11" t="inlineStr">
-        <is>
-          <t>参照リンク</t>
-        </is>
-      </c>
-      <c r="C245" s="10" t="inlineStr"/>
+      <c r="A245" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>権限母体 ｜ 経理・人事など複数の権限を派生させるための、共通の土台となる権限</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>箇条書き</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>・[ラクミー経営管理 ログイン](https://manager.rakmy.jp/users/sign_in)</t>
+          <t>権限一覧 ｜ 作った権限を、画面ごとの設定とあわせて一覧で見比べる画面</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr"/>
@@ -3905,12 +3909,12 @@
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>箇条書き</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>・[店舗の登録方法](https://help.rakmy.jp/management/店舗)</t>
+          <t>役割サマリ ｜ 権限ごとに、何名に割り当てているかを確認する画面</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr"/>
@@ -3918,18 +3922,83 @@
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
+          <t>指標 ｜ 売上・原価・人件費など、画面に表示される数字のこと</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>「役職」は従業員情報に登録された肩書きで、権限とは別のものです。役職を変更しても権限は変わりません。</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B250" s="11" t="inlineStr">
+        <is>
+          <t>参照リンク</t>
+        </is>
+      </c>
+      <c r="C250" s="10" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="4" t="inlineStr">
+        <is>
+          <t>箇条書き</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>・[ラクミー経営管理 ログイン](https://manager.rakmy.jp/users/sign_in)</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="4" t="inlineStr">
+        <is>
+          <t>箇条書き</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>・[店舗の登録方法](https://help.rakmy.jp/management/店舗)</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B253" s="4" t="inlineStr">
+        <is>
           <t>サポートが必要ですか？ [サポートチームに連絡](https://docs.google.com/forms/d/e/1FAIpQLSe1qwnma82vLEpQQNdzjl_gLSt_qHMHZp6eqmhaziUB11IAOA/viewform)</t>
         </is>
       </c>
-      <c r="C248" s="4" t="inlineStr"/>
+      <c r="C253" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C248"/>
+  <autoFilter ref="A2:C253"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/20260806_権限設定_ヘルプページ.xlsx
+++ b/20260806_権限設定_ヘルプページ.xlsx
@@ -1581,30 +1581,30 @@
       <c r="C76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="12" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>雛形は3つに分かれています。</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B77" s="13" t="inlineStr">
-        <is>
-          <t>雛形 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C77" s="12" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>本部管理 ｜ 全社の設定・一覧を操作／閲覧できます</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr"/>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>分類 ｜ 中身 ｜ どんなときに選ぶか</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>店長 ｜ 自店舗の設定・一覧を操作／閲覧できます</t>
+          <t>スタンダードテンプレ ｜ 全権オーナー相当／本部管理／店長／従業員 ｜ はじめて作るとき。近いものを選んで違うところだけ直します</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr"/>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>従業員 ｜ 閲覧が中心です</t>
+          <t>カスタマイズテンプレ ｜ 貴社で作った権限（経理担当・エリアマネージャー など） ｜ 似た権限をもう1つ作るとき。作った権限は自動でここに並びます</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr"/>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>既存の権限をコピー ｜ 運用中の権限を複製して、一部だけ変更できます</t>
+          <t>新規作成 ｜ すべて「なし」の状態 ｜ ゼロから決めたいとき</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr"/>
@@ -1648,12 +1648,12 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>まっさら（なし） ｜ すべて「なし」の状態から設定します</t>
+          <t>一度作った権限は、次の土台になります。 たとえば「エリアマネージャー」を作ると、次からはカスタマイズテンプレに並び、そこから「西エリアマネージャー」を作れます。</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr"/>

--- a/20260806_権限設定_ヘルプページ.xlsx
+++ b/20260806_権限設定_ヘルプページ.xlsx
@@ -1791,7 +1791,7 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>区分によって設定できる画面が変わります。保存したあとに区分を変更することはできません。別の区分の権限が必要になった場合は、新しく作成してください。「既存の権限をコピー」を使うと、設定を引き継いだうえで区分だけ変えられます。</t>
+          <t>区分によって設定できる画面が変わります。保存したあとに区分を変更することはできません。別の区分の権限が必要になった場合は、新しく作成してください。カスタマイズテンプレから元の権限を選ぶと、設定を引き継いだうえで区分だけ変えられます。</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>&gt; 権限の修正は、その権限をお持ちの全員に反映されますのでご注意ください。特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
+          <t>&gt; 権限の修正は、その権限をお持ちの全員に反映されますのでご注意ください。特定の方だけ変更したい場合は、権限を修正するのではなく、カスタマイズテンプレから元の権限を選んで新しい権限を作成し、その方に割り当ててください。</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr"/>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="C227" s="18" t="inlineStr">
         <is>
-          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
+          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、カスタマイズテンプレから元の権限を選んで新しい権限を作成し、その方に割り当ててください。</t>
         </is>
       </c>
     </row>
